--- a/신성텍 부적합 현황.xlsx
+++ b/신성텍 부적합 현황.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\POWER BI\신성텍\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE50F47-4DC7-42D4-806F-815D9256CAB3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919259B2-CAFB-4F09-A74A-17DA9FE77D45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7FBDE3CB-3BE6-4858-BD36-C283BF315A42}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7FBDE3CB-3BE6-4858-BD36-C283BF315A42}"/>
   </bookViews>
   <sheets>
     <sheet name="사내불량" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
   <si>
     <t>품명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,6 +410,10 @@
   </si>
   <si>
     <t xml:space="preserve">조치 내용 및 특이사항  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -2517,7 +2521,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="21">
-        <f t="shared" ref="H4:H8" si="0">G4/F4</f>
+        <f t="shared" ref="H4:H9" si="0">G4/F4</f>
         <v>0.1</v>
       </c>
       <c r="I4" s="9"/>
@@ -2663,14 +2667,31 @@
       <c r="O8" s="9"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="11"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="9"/>
+      <c r="B9" s="11">
+        <v>46075</v>
+      </c>
+      <c r="C9" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="F9" s="16">
+        <v>200</v>
+      </c>
+      <c r="G9" s="6">
+        <v>200</v>
+      </c>
+      <c r="H9" s="6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="9">
+        <v>200</v>
+      </c>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>

--- a/신성텍 부적합 현황.xlsx
+++ b/신성텍 부적합 현황.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="N:\개인\POWER BI\신성텍\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김훈희\Downloads\shinsung-ncp-management-main\shinsung-ncp-management-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{919259B2-CAFB-4F09-A74A-17DA9FE77D45}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{7FBDE3CB-3BE6-4858-BD36-C283BF315A42}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12165"/>
   </bookViews>
   <sheets>
     <sheet name="사내불량" sheetId="1" r:id="rId1"/>
@@ -18,9 +17,9 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">사내불량!$B$3:$Q$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">사외불량!$B$3:$O$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">사외불량!$B$3:$O$29</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
   <si>
     <t>품명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -410,21 +409,13 @@
   </si>
   <si>
     <t xml:space="preserve">조치 내용 및 특이사항  </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="176" formatCode="0_);[Red]\(0\)"/>
     <numFmt numFmtId="177" formatCode="0.0%"/>
@@ -745,7 +736,7 @@
   <cellStyles count="3">
     <cellStyle name="좋음" xfId="1" builtinId="26"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="표준 2" xfId="2" xr:uid="{6A43DEF7-85D8-4543-9B81-6299C071B7EB}"/>
+    <cellStyle name="표준 2" xfId="2"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1076,8 +1067,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99BC34A0-7885-4B17-9A44-9155E3A920C9}">
-  <dimension ref="B1:S1039696"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B1:S1039695"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
@@ -2349,62 +2340,20 @@
       </c>
       <c r="S30" s="27"/>
     </row>
-    <row r="31" spans="2:19">
-      <c r="B31" s="11">
-        <v>46075</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>55</v>
-      </c>
-      <c r="E31" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="F31" s="22">
-        <v>300</v>
-      </c>
-      <c r="G31" s="7">
-        <v>320</v>
-      </c>
-      <c r="H31" s="6">
-        <f t="shared" ref="H31" si="2">SUM(J31:Q31)</f>
-        <v>300</v>
-      </c>
-      <c r="I31" s="25">
-        <f t="shared" ref="I31" si="3">H31/G31</f>
-        <v>0.9375</v>
-      </c>
-      <c r="J31" s="9">
-        <v>300</v>
-      </c>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-      <c r="O31" s="9"/>
-      <c r="P31" s="9"/>
-      <c r="Q31" s="9"/>
-      <c r="R31" s="30" t="s">
-        <v>106</v>
-      </c>
-      <c r="S31" s="27"/>
-    </row>
-    <row r="62656" spans="2:3">
-      <c r="B62656" s="12"/>
-      <c r="C62656" s="12"/>
-    </row>
-    <row r="1027652" spans="2:3">
-      <c r="B1027652" s="13"/>
-      <c r="C1027652" s="17"/>
-    </row>
-    <row r="1039696" spans="2:3">
-      <c r="B1039696" s="13"/>
-      <c r="C1039696" s="17"/>
+    <row r="62655" spans="2:3">
+      <c r="B62655" s="12"/>
+      <c r="C62655" s="12"/>
+    </row>
+    <row r="1027651" spans="2:3">
+      <c r="B1027651" s="13"/>
+      <c r="C1027651" s="17"/>
+    </row>
+    <row r="1039695" spans="2:3">
+      <c r="B1039695" s="13"/>
+      <c r="C1039695" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:Q30" xr:uid="{99BC34A0-7885-4B17-9A44-9155E3A920C9}"/>
+  <autoFilter ref="B3:Q30"/>
   <mergeCells count="3">
     <mergeCell ref="J2:Q2"/>
     <mergeCell ref="B2:H2"/>
@@ -2417,8 +2366,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0558E418-2F72-447F-AC34-F245B2DBF6B5}">
-  <dimension ref="B2:O1039943"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="B2:O1039942"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="3.125" customWidth="1"/>
@@ -2521,7 +2470,7 @@
         <v>1</v>
       </c>
       <c r="H4" s="21">
-        <f t="shared" ref="H4:H9" si="0">G4/F4</f>
+        <f t="shared" ref="H4:H8" si="0">G4/F4</f>
         <v>0.1</v>
       </c>
       <c r="I4" s="9"/>
@@ -2667,31 +2616,14 @@
       <c r="O8" s="9"/>
     </row>
     <row r="9" spans="2:15">
-      <c r="B9" s="11">
-        <v>46075</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>109</v>
-      </c>
-      <c r="D9" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="F9" s="16">
-        <v>200</v>
-      </c>
-      <c r="G9" s="6">
-        <v>200</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="I9" s="9">
-        <v>200</v>
-      </c>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="9"/>
       <c r="J9" s="9"/>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
@@ -2990,11 +2922,11 @@
     <row r="28" spans="2:15">
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="3"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
+      <c r="D28" s="22"/>
+      <c r="E28" s="22"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="7"/>
       <c r="I28" s="9"/>
       <c r="J28" s="9"/>
       <c r="K28" s="9"/>
@@ -3019,21 +2951,8 @@
       <c r="N29" s="9"/>
       <c r="O29" s="9"/>
     </row>
-    <row r="30" spans="2:15">
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="4"/>
-      <c r="G30" s="7"/>
-      <c r="H30" s="7"/>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
+    <row r="40" spans="9:9">
+      <c r="I40"/>
     </row>
     <row r="41" spans="9:9">
       <c r="I41"/>
@@ -3089,23 +3008,20 @@
     <row r="58" spans="9:9">
       <c r="I58"/>
     </row>
-    <row r="59" spans="9:9">
-      <c r="I59"/>
-    </row>
-    <row r="62903" spans="2:3">
-      <c r="B62903" s="12"/>
-      <c r="C62903" s="12"/>
-    </row>
-    <row r="1027899" spans="2:3">
-      <c r="B1027899" s="13"/>
-      <c r="C1027899" s="17"/>
-    </row>
-    <row r="1039943" spans="2:3">
-      <c r="B1039943" s="13"/>
-      <c r="C1039943" s="17"/>
+    <row r="62902" spans="2:3">
+      <c r="B62902" s="12"/>
+      <c r="C62902" s="12"/>
+    </row>
+    <row r="1027898" spans="2:3">
+      <c r="B1027898" s="13"/>
+      <c r="C1027898" s="17"/>
+    </row>
+    <row r="1039942" spans="2:3">
+      <c r="B1039942" s="13"/>
+      <c r="C1039942" s="17"/>
     </row>
   </sheetData>
-  <autoFilter ref="B3:O30" xr:uid="{99BC34A0-7885-4B17-9A44-9155E3A920C9}"/>
+  <autoFilter ref="B3:O29"/>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="I2:O2"/>

--- a/신성텍 부적합 현황.xlsx
+++ b/신성텍 부적합 현황.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김훈희\Downloads\shinsung-ncp-management-main\shinsung-ncp-management-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\김훈희\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="109">
   <si>
     <t>품명</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -409,6 +409,10 @@
   </si>
   <si>
     <t xml:space="preserve">조치 내용 및 특이사항  </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>김훈희</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1240,7 +1244,7 @@
         <v>91</v>
       </c>
       <c r="I5" s="25">
-        <f t="shared" ref="I5:I30" si="1">H5/G5</f>
+        <f t="shared" ref="I5:I31" si="1">H5/G5</f>
         <v>0.15397631133671744</v>
       </c>
       <c r="J5" s="9">
@@ -2339,6 +2343,36 @@
         <v>106</v>
       </c>
       <c r="S30" s="27"/>
+    </row>
+    <row r="31" spans="2:19">
+      <c r="B31" s="14">
+        <v>46076</v>
+      </c>
+      <c r="C31" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" s="2">
+        <v>1234</v>
+      </c>
+      <c r="E31" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="F31" s="23">
+        <v>500</v>
+      </c>
+      <c r="G31" s="8">
+        <v>100</v>
+      </c>
+      <c r="H31" s="8">
+        <v>100</v>
+      </c>
+      <c r="I31" s="25">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J31" s="10">
+        <v>100</v>
+      </c>
     </row>
     <row r="62655" spans="2:3">
       <c r="B62655" s="12"/>
